--- a/プリントアース_LINEOA_配信企画案_2026-09.xlsx
+++ b/プリントアース_LINEOA_配信企画案_2026-09.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1179,165 +1179,65 @@
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>2026/09/25</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>2026/09/24</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>草案作成中</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>セグメント配信</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>冬コミ・同人誌</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>推し活・同人・トレカ関連URLのクリック者だけに配信する。BtoB層に同人の話を送るとブロックされるため、分けること自体が目的。冬コミの入稿ピーク前に先回りして枠を押さえる。</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>通常配信</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>新商品・トレカ台紙／推し活グッズ</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Meta広告の主力フックである推し活を、LINE側でも正面から扱う唯一の全員配信。新商品告知は開封理由になり、BtoC層に「この会社は自分向けでもある」と認識させる役割を持つ（現状ここが弱くブロック要因になっている）。</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>CV獲得</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>BtoC・同人作家・クリエイター（Meta広告流入層）</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>推し活／同人／トレカ／うちわ のURLクリック者</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>BtoC・推し活層・TCGショップ・同人＋BtoBのノベルティ担当</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1040×1040 px</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>トレカ台紙バナーの路線（ピンク×パープル、キラキラ、ポップ）。同人誌の実物写真＋「表紙PP加工」などの仕様バッジ。「1種類1冊から」を必ず入れる。下部CTA帯。</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>冬コミの本、いつ入稿しますか。
-12月直前は混み合うので、
-10月中に出しておくと安心です。
-1種類1冊から刷れます。
-表紙の加工も選べます。
-同人誌印刷を見る（CTA）</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>※最小ロットと加工オプションを要確認</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.inkart.jp/lineup/doujinshi-all/</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>LINEOA</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>crm</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>20260925_message_WinterComike</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.inkart.jp/lineup/doujinshi-all/?utm_source=LINEOA&amp;utm_medium=crm&amp;utm_campaign=20260925_message_WinterComike</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="150" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2026/09/28</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>草案作成中</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>通常配信</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>新商品・トレカ台紙／推し活グッズ</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Meta広告の主力フックである推し活を、LINE側でも正面から扱う唯一の全員配信。新商品告知は開封理由になり、BtoC層に「この会社は自分向けでもある」と認識させる役割を持つ（現状ここが弱くブロック要因になっている）。</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>CV獲得</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>BtoC・推し活層・TCGショップ・同人＋BtoBのノベルティ担当</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>全員</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1040×1040 px</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>既存のトレカ台紙バナーを流用可。4タイプ（A〜D）の並列構成はそのまま活かす。「1種類1枚から」を追加。下部CTA帯を赤に統一。</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>推しのカード、
 そのまま渡すのはもったいない。
@@ -1348,14 +1248,116 @@
 台紙を見る（CTA）</t>
         </is>
       </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>※既存バナー流用可</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.inkart.jp/lineup/trading_card_all/</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>LINEOA</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>crm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>20260929_message_TradingCardMount</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.inkart.jp/lineup/trading_card_all/?utm_source=LINEOA&amp;utm_medium=crm&amp;utm_campaign=20260929_message_TradingCardMount</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>要確定</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>要確定</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>草案作成中</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>通常配信</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>◯◯キャンペーン（開始告知）</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>期間限定の割引を告知して、期間全体の注文を立ち上げる。「データのご入稿は後から」を最初から明示し、初動の摩擦を消す。</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>キャンペーン訴求</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>BtoB・店舗・法人（対象商材が名刺・チラシ・冊子のため）</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1040×1040 px</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>※トンマナは後日確定。季節モチーフ背景／左上に黄丸で割引率／中央に対象商材／下部CTA帯／右下に期限</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>◯◯キャンペーン、今日から始まります。
+最大◯%OFF。
+対象は名刺・ショップカード、
+チラシ・フライヤー、冊子です。
+◯月◯日まで。
+データのご入稿は後からで大丈夫です。
+先にご注文だけ進めておけます。
+対象商品を見る（CTA）</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>※既存バナー流用可</t>
+          <t>※キャンペーン名・期間・割引率が未確定</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.inkart.jp/lineup/trading_card_all/</t>
+          <t>https://www.inkart.jp/cp/renewal/</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1370,12 +1372,213 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>20260929_message_TradingCardMount</t>
+          <t>2026MMDD_message_◯◯Campaign</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>https://www.inkart.jp/lineup/trading_card_all/?utm_source=LINEOA&amp;utm_medium=crm&amp;utm_campaign=20260929_message_TradingCardMount</t>
+          <t>https://www.inkart.jp/cp/renewal/?utm_source=LINEOA&amp;utm_medium=crm&amp;utm_campaign=2026MMDD_message_◯◯Campaign</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>要確定</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>要確定</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>草案作成中</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>通常配信</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>◯◯キャンペーン（中盤リマインド）</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>「あとで」と先送りした層を動かす。残り日数を明示して締切を意識させる。</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>キャンペーン訴求</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>BtoB・店舗・法人</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1040×1040 px</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>※開始告知のバナーを流用し、左上を「残り◯日」に差し替え</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>◯◯キャンペーン、残り◯日です。
+最大◯%OFF。
+名刺・チラシ・冊子が対象です。
+「あとで」と思っていた方、
+そろそろ動いておいてください。
+◯月◯日で終わります。
+対象商品を見る（CTA）</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>※開始告知バナーの流用で制作コストを抑える</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.inkart.jp/cp/renewal/</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>LINEOA</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>crm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026MMDD_message_◯◯CampaignRemind</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.inkart.jp/cp/renewal/?utm_source=LINEOA&amp;utm_medium=crm&amp;utm_campaign=2026MMDD_message_◯◯CampaignRemind</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>要確定</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>要確定</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>草案作成中</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>通常配信</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>◯◯キャンペーン（最終日リマインド）</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>最終日の離脱理由の大半は「データが間に合わない」。注文と入稿を切り離せることを明示して、そこだけを潰す。</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>キャンペーン訴求</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>BtoB・店舗・法人</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1040×1040 px</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>※中盤バナーの「残り◯日」を「本日終了」に差し替え</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>本日23:59で終了します。
+◯◯キャンペーン、最大◯%OFF。
+今日中のご注文までが対象です。
+データはまだ無くても大丈夫です。
+ご注文だけ先に済ませてください。
+今すぐ注文する（CTA）</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>※終了時刻（23:59か締切時間か）を要確認</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.inkart.jp/cp/renewal/</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>LINEOA</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>crm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026MMDD_message_◯◯CampaignLast</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.inkart.jp/cp/renewal/?utm_source=LINEOA&amp;utm_medium=crm&amp;utm_campaign=2026MMDD_message_◯◯CampaignLast</t>
         </is>
       </c>
     </row>
